--- a/feedback_forms/013_sports_equipment_satisfaction_survey--feedback_forms.xlsx
+++ b/feedback_forms/013_sports_equipment_satisfaction_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -838,8 +838,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -867,12 +867,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'treadmill'}</t>
+          <t>treadmill</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Treadmill'}</t>
+          <t>Treadmill</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'stationary_bike'}</t>
+          <t>stationary_bike</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Stationary Bike'}</t>
+          <t>Stationary Bike</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'free_weights'}</t>
+          <t>free_weights</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Free Weights'}</t>
+          <t>Free Weights</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'resistance_bands'}</t>
+          <t>resistance_bands</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Resistance Bands'}</t>
+          <t>Resistance Bands</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'yoga_ball'}</t>
+          <t>yoga_ball</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Yoga Ball'}</t>
+          <t>Yoga Ball</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'please_select_one'}</t>
+          <t>please_select_one</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Please select one'}</t>
+          <t>Please select one</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Very Poor'}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Very Poor'}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Maybe'}</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'physical_fitness'}</t>
+          <t>physical_fitness</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Physical Fitness'}</t>
+          <t>Physical Fitness</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'yoga_or_pilates'}</t>
+          <t>yoga_or_pilates</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Yoga or Pilates'}</t>
+          <t>Yoga or Pilates</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'strength_training'}</t>
+          <t>strength_training</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Strength Training'}</t>
+          <t>Strength Training</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'stretching_or_flexibility'}</t>
+          <t>stretching_or_flexibility</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Stretching or Flexibility'}</t>
+          <t>Stretching or Flexibility</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'rehabilitation'}</t>
+          <t>rehabilitation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Rehabilitation'}</t>
+          <t>Rehabilitation</t>
         </is>
       </c>
     </row>
